--- a/SS_rubblemound_input.xlsx
+++ b/SS_rubblemound_input.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\0_StormSim_Task\StormSim-Library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6386C7D3-94C4-4397-A294-8BC426E14037}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA2DA920-2572-4877-AF7D-906AF5CA3069}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8970" yWindow="5280" windowWidth="28800" windowHeight="15345" xr2:uid="{DF680589-5370-4D92-A3AE-D910B140CCC4}"/>
+    <workbookView xWindow="4650" yWindow="810" windowWidth="28800" windowHeight="15255" xr2:uid="{DF680589-5370-4D92-A3AE-D910B140CCC4}"/>
   </bookViews>
   <sheets>
     <sheet name="Rubblemound" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>compute_damaging_depth_slope</t>
-  </si>
-  <si>
     <t>Shielding Parameter To Use For Damaging Depths</t>
   </si>
   <si>
@@ -488,9 +485,6 @@
     <t>csr_compute_S_submerged</t>
   </si>
   <si>
-    <t>Bottom Slope To Use For Damaging Depths (tanb)</t>
-  </si>
-  <si>
     <t>compute_dn50_submerged</t>
   </si>
   <si>
@@ -501,6 +495,12 @@
   </si>
   <si>
     <t>..\CHS_Dependencies</t>
+  </si>
+  <si>
+    <t>offshore_slope</t>
+  </si>
+  <si>
+    <t>Offshore slope (cota)</t>
   </si>
 </sst>
 </file>
@@ -543,7 +543,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -571,12 +571,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -611,7 +605,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -768,11 +762,42 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -831,54 +856,65 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1194,211 +1230,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{710E9416-AE2D-4233-9805-411704AE5E86}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.7109375" customWidth="1"/>
     <col min="2" max="2" width="53.5703125" customWidth="1"/>
     <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="153.42578125" customWidth="1"/>
-    <col min="6" max="6" width="28.42578125" customWidth="1"/>
+    <col min="6" max="6" width="45" customWidth="1"/>
     <col min="7" max="7" width="84.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="46.140625" customWidth="1"/>
     <col min="9" max="9" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-      <c r="F1" s="45" t="s">
-        <v>111</v>
-      </c>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44" t="s">
-        <v>110</v>
-      </c>
-      <c r="I1" s="44" t="s">
-        <v>110</v>
-      </c>
+      <c r="A1" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="F1" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
     </row>
     <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="H2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>17</v>
-      </c>
       <c r="I2" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>105</v>
+        <v>14</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>104</v>
+        <v>13</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>0</v>
       </c>
       <c r="I3" s="6">
-        <v>1000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>100</v>
+        <v>11</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>99</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>50</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-    </row>
-    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="G6" s="38"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
-    </row>
-    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="10" t="s">
-        <v>16</v>
+        <v>129</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="F8" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="I8" s="18">
-        <v>0</v>
+        <v>126</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>0</v>
@@ -1407,120 +1453,118 @@
         <v>1</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>87</v>
+        <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B10" s="26" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="D10" s="24">
+      <c r="B10" s="48" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="D10" s="50">
         <v>3</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>149</v>
+        <v>4</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>148</v>
+        <v>3</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="I10" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="B11" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="B11" s="48" t="s">
         <v>120</v>
       </c>
+      <c r="C11" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="D11" s="50" t="s">
+        <v>119</v>
+      </c>
       <c r="F11" s="5" t="s">
-        <v>85</v>
+        <v>2</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>0</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="B12" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="2">
+      <c r="B12" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="50">
         <v>176.45</v>
       </c>
-      <c r="F12" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="I12" s="30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2">
-        <v>0</v>
-      </c>
-      <c r="F13" s="38"/>
+      <c r="B13" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="D13" s="50">
+        <v>0</v>
+      </c>
+      <c r="F13" s="39" t="s">
+        <v>110</v>
+      </c>
       <c r="G13" s="38"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
+      <c r="H13" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="I13" s="38" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>0</v>
@@ -1528,19 +1572,25 @@
       <c r="D14" s="2">
         <v>1</v>
       </c>
-      <c r="F14" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-    </row>
-    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F14" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>0</v>
@@ -1548,25 +1598,25 @@
       <c r="D15" s="2">
         <v>0</v>
       </c>
-      <c r="F15" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>16</v>
+      <c r="F15" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="I15" s="6">
+        <v>1000</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>0</v>
@@ -1574,25 +1624,25 @@
       <c r="D16" s="2">
         <v>1</v>
       </c>
-      <c r="F16" s="34" t="s">
-        <v>74</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="I16" s="18">
-        <v>1</v>
+      <c r="F16" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="I16" s="2">
+        <v>50</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>0</v>
@@ -1600,25 +1650,17 @@
       <c r="D17" s="2">
         <v>0</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38"/>
+    </row>
+    <row r="18" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>0</v>
@@ -1626,25 +1668,19 @@
       <c r="D18" s="2">
         <v>0</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F18" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>0</v>
@@ -1652,25 +1688,25 @@
       <c r="D19" s="2">
         <v>1</v>
       </c>
-      <c r="F19" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I19" s="2">
-        <v>1</v>
+      <c r="F19" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>0</v>
@@ -1678,219 +1714,349 @@
       <c r="D20" s="2">
         <v>1</v>
       </c>
-      <c r="F20" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="I20" s="2">
+      <c r="F20" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I20" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="31" t="s">
-        <v>93</v>
+      <c r="A21" s="25" t="s">
+        <v>92</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C21" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="D21" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="F21" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="G21" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="H21" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="I21" s="30">
+      <c r="D21" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="36"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="F22" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I22" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="42"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
-    </row>
     <row r="23" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="33"/>
+      <c r="A23" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="27"/>
+      <c r="C23" s="27"/>
+      <c r="D23" s="27"/>
+      <c r="F23" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I23" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="I24" s="24">
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="21" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C25" s="35" t="s">
         <v>81</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>80</v>
       </c>
       <c r="D25" s="18">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F25" s="32"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+    </row>
+    <row r="26" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C26" s="35" t="s">
         <v>76</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>75</v>
       </c>
       <c r="D26" s="18">
         <v>2.46</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F26" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+    </row>
+    <row r="27" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B27" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="C27" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="D27" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="B27" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="C27" s="35" t="s">
-        <v>0</v>
-      </c>
-      <c r="D27" s="18" t="s">
-        <v>154</v>
+      <c r="F27" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F28" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="G28" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>70</v>
+      <c r="H28" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="I28" s="18">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>65</v>
+      <c r="H29" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I29" s="2">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="33"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="33"/>
-      <c r="D30" s="33"/>
+      <c r="A30" s="27"/>
+      <c r="B30" s="27"/>
+      <c r="C30" s="27"/>
+      <c r="D30" s="27"/>
+      <c r="F30" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I30" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="F31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
+      <c r="H31" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I31" s="2">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33" s="45" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="47">
+        <v>180.1</v>
+      </c>
+      <c r="F33" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G33" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="B33" s="29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C33" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" s="27">
-        <v>180.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="H33" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="I33" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="C34" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="24">
+      <c r="B34" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C34" s="49" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" s="50">
         <v>0.3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D35" s="2">
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>0</v>
@@ -1899,12 +2065,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>0</v>
@@ -1913,152 +2079,153 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="23"/>
-    </row>
-    <row r="39" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-    </row>
-    <row r="40" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B40" s="10" t="s">
+    <row r="38" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="41" t="s">
+        <v>153</v>
+      </c>
+      <c r="B38" s="42" t="s">
+        <v>154</v>
+      </c>
+      <c r="C38" s="43" t="s">
+        <v>0</v>
+      </c>
+      <c r="D38" s="44">
+        <f>1/8</f>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+    </row>
+    <row r="40" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+    </row>
+    <row r="41" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="B41" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="C41" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B41" s="20" t="s">
+      <c r="D41" s="10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="D41" s="18">
+      <c r="B42" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="D42" s="18">
         <v>1.65</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="4" t="s">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D42" s="2">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="5" t="s">
+      <c r="B43" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>38</v>
-      </c>
       <c r="C43" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D43" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>36</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="D44" s="2">
         <v>1000</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="D45" s="2">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D45" s="2">
+      <c r="C46" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D46" s="2">
         <v>0.4</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="B46" s="4" t="s">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D46" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="5" t="s">
+      <c r="B47" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="C47" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D47" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="5" t="s">
+      <c r="B48" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B48" s="4" t="s">
-        <v>25</v>
-      </c>
       <c r="C48" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D48" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B49" s="4" t="s">
         <v>24</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>23</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>0</v>
@@ -2067,200 +2234,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="50" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="17" t="s">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="C50" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D50" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C50" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="D50" s="14">
+      <c r="B51" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="D51" s="14">
         <v>0.9</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-    </row>
-    <row r="52" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-    </row>
-    <row r="53" spans="1:4" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="B53" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D53" s="10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="D54" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D56" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D57" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D58" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D59" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D60" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D62" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D63" s="2">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="13"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+    </row>
+    <row r="53" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <sheetProtection formatColumns="0" selectLockedCells="1"/>
   <protectedRanges>
-    <protectedRange sqref="I3:I4 I8:I9 I11:I12 I16" name="Range1_1"/>
-    <protectedRange sqref="D50 D41:D45" name="Range1_1_4"/>
-    <protectedRange sqref="D46:D48" name="Range1_1_4_1"/>
+    <protectedRange sqref="I15:I16 I20:I21 I23:I24 I28" name="Range1_1"/>
+    <protectedRange sqref="D51 D42:D46" name="Range1_1_4"/>
+    <protectedRange sqref="D47:D49" name="Range1_1_4_1"/>
     <protectedRange sqref="D14 D16:D18 D9:D12 D6" name="Range1_1_1"/>
     <protectedRange sqref="D8 D15" name="Range1_1_1_1"/>
     <protectedRange sqref="D13" name="Range1_1_2"/>
@@ -2276,7 +2292,7 @@
     <protectedRange sqref="D34" name="Range1_1_3_1_4"/>
     <protectedRange sqref="D35" name="Range1_1_3_1_5"/>
     <protectedRange sqref="D36" name="Range1_1_3_1_7"/>
-    <protectedRange sqref="D37" name="Range1_1_3_1_8"/>
+    <protectedRange sqref="D37:D38" name="Range1_1_3_1_8"/>
   </protectedRanges>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
